--- a/data/trans_dic/P19D_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,82; 89,27</t>
+          <t>84,7; 89,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,3; 76,4</t>
+          <t>70,15; 76,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,52; 89,06</t>
+          <t>82,43; 89,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,94; 85,32</t>
+          <t>79,4; 85,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,12; 91,97</t>
+          <t>87,97; 91,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,22; 86,58</t>
+          <t>82,37; 86,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,01; 89,65</t>
+          <t>84,46; 89,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,1; 89,85</t>
+          <t>86,38; 90,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,11; 90,43</t>
+          <t>87,24; 90,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,25; 81,85</t>
+          <t>78,12; 81,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,47; 88,59</t>
+          <t>84,4; 88,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,77; 87,39</t>
+          <t>84,37; 87,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,87; 95,46</t>
+          <t>92,87; 95,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,23; 91,23</t>
+          <t>87,94; 91,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,38; 91,42</t>
+          <t>88,33; 91,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,04; 92,82</t>
+          <t>90,48; 93,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,61; 95,17</t>
+          <t>92,57; 95,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,05</t>
+          <t>89,04; 92,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,88; 92,51</t>
+          <t>89,77; 92,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,99; 97,2</t>
+          <t>94,22; 95,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93,11; 94,95</t>
+          <t>93,16; 94,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 91,23</t>
+          <t>89,13; 91,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,55; 91,58</t>
+          <t>89,62; 91,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,52; 94,65</t>
+          <t>92,51; 94,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,28; 98,04</t>
+          <t>93,99; 98,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94,12; 98,07</t>
+          <t>94,33; 98,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95,12; 98,36</t>
+          <t>95,3; 98,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95,62; 98,52</t>
+          <t>94,54; 98,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,74; 98,22</t>
+          <t>94,65; 98,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,43; 96,88</t>
+          <t>92,93; 97,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,99; 96,89</t>
+          <t>93,1; 96,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,51; 98,67</t>
+          <t>96,76; 98,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,27; 97,81</t>
+          <t>95,35; 97,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,16; 97,14</t>
+          <t>94,26; 97,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94,91; 97,32</t>
+          <t>94,67; 97,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>96,5; 98,3</t>
+          <t>96,2; 98,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,65; 93,72</t>
+          <t>91,57; 93,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,97; 87,55</t>
+          <t>85,03; 87,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,43; 91,68</t>
+          <t>89,45; 91,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,28; 92,26</t>
+          <t>90,33; 92,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,04; 93,99</t>
+          <t>91,98; 93,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,89; 90,16</t>
+          <t>87,9; 90,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,9; 92,05</t>
+          <t>89,93; 92,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,78; 95,6</t>
+          <t>93,42; 94,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,14; 93,52</t>
+          <t>92,12; 93,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86,85; 88,64</t>
+          <t>87,0; 88,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,09; 91,6</t>
+          <t>90,0; 91,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,11; 93,6</t>
+          <t>92,27; 93,46</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399545</t>
+          <t>443304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>636777</t>
+          <t>693992</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1036322</t>
+          <t>1137295</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>578553; 616168</t>
+          <t>584582; 617836</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>548547; 596098</t>
+          <t>547396; 596451</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>377464; 407383</t>
+          <t>377071; 407212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>381491; 412323</t>
+          <t>425686; 458714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>845001; 881969</t>
+          <t>843632; 882145</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>928644; 977888</t>
+          <t>930345; 980480</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>535656; 571584</t>
+          <t>538500; 572652</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>616517; 650952</t>
+          <t>679348; 708027</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1436536; 1491339</t>
+          <t>1438660; 1489383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1494236; 1563151</t>
+          <t>1491890; 1563156</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>924966; 970046</t>
+          <t>924204; 971652</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1011817; 1055516</t>
+          <t>1115803; 1156857</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1832939</t>
+          <t>1972644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2108989</t>
+          <t>2006735</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3941928</t>
+          <t>3979380</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1220671; 1254822</t>
+          <t>1220683; 1255483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1485122; 1535553</t>
+          <t>1480098; 1533581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1498509; 1550115</t>
+          <t>1497756; 1549474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1361955; 2071274</t>
+          <t>1941987; 2003246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1271705; 1306920</t>
+          <t>1271120; 1306416</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1412620; 1461041</t>
+          <t>1413335; 1463311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1535776; 1580760</t>
+          <t>1533887; 1582371</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2087205; 2135671</t>
+          <t>1987715; 2023301</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2502565; 2552043</t>
+          <t>2503892; 2552734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2914234; 2983637</t>
+          <t>2914913; 2981453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3048677; 3117761</t>
+          <t>3051081; 3118628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3211499; 4191604</t>
+          <t>3937388; 4012533</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614765</t>
+          <t>680139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>638776</t>
+          <t>710562</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1253540</t>
+          <t>1390701</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>426544; 443577</t>
+          <t>425229; 443941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>413194; 430525</t>
+          <t>414095; 431388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>474018; 490154</t>
+          <t>474914; 490643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604341; 622652</t>
+          <t>664448; 689292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>387268; 401496</t>
+          <t>386917; 401858</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>390763; 409591</t>
+          <t>392856; 410129</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>472677; 492535</t>
+          <t>473257; 492363</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>630760; 644843</t>
+          <t>702896; 717085</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>820488; 842340</t>
+          <t>821200; 843541</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>811454; 837086</t>
+          <t>812303; 837602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>955366; 979654</t>
+          <t>953020; 978984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1240555; 1263750</t>
+          <t>1374976; 1401377</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2847249</t>
+          <t>3096087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3384542</t>
+          <t>3411289</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6231791</t>
+          <t>6507376</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2251886; 2302857</t>
+          <t>2249837; 2300234</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2466205; 2540954</t>
+          <t>2467854; 2542514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2371032; 2430721</t>
+          <t>2371466; 2429536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2184806; 3087613</t>
+          <t>3057861; 3132655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2522663; 2576218</t>
+          <t>2521152; 2574645</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2759135; 2830329</t>
+          <t>2759564; 2829881</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2566359; 2627817</t>
+          <t>2567140; 2629057</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3353106; 3417854</t>
+          <t>3384122; 3433813</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4789258; 4861204</t>
+          <t>4788556; 4865565</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5247452; 5355789</t>
+          <t>5256248; 5357110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4960468; 5043335</t>
+          <t>4955582; 5046254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5406879; 6479094</t>
+          <t>6465988; 6549187</t>
         </is>
       </c>
     </row>
